--- a/extenbooks/S404_extenbook.xlsx
+++ b/extenbooks/S404_extenbook.xlsx
@@ -1346,7 +1346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A132"/>
+  <dimension ref="A1:A136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1378,14 +1378,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>**Data Provenance Record (DPR)**</t>
+          <t>**Data Provenance Record (DPR)** — the internal, full-provenance companion to the public Explainer.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>**Phase**: 5 (Ingestion)</t>
+          <t>**Record type**: Data Provenance Record (source-and-construction detail)</t>
         </is>
       </c>
     </row>
@@ -1409,7 +1409,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>&gt; **Recovery (2026-05-26):** Recovered from data_unavailable by native-resolution vector trace of Shaikh Fig 4.19 Unit Labor Cost (= Inman 1995) from the book PDF (Robert _PDF_LIBRARY p204-205), overlay-validated vs the figure. content_type=theoretical (Monte-Carlo simulation curve), x=annual vehicle output; chopped keys on point-index per the S308 functional-curve precedent. provenance: digitized. V03 round-trip PASS; pipeline + anu-doctor 0/0. Source: SalvagedInputs/book_data/Reconstructed/Inman_1995_S404-407_cost_curves.json; method: Technical/WL1_Tsoulfidis_Tsaliki/EXTRACTION_REPORT.md.</t>
+          <t>&gt; **Recovery (2026-05-26):** This curve was previously marked as having no available underlying data. It was recovered by digitizing Shaikh's Figure 4.19 (Automotive Unit Labor Cost, which reproduces Inman 1995) from the source-book scan at native resolution, then overlay-checking the digitized points against the printed figure. It is a theoretical curve (the mean of a Monte-Carlo simulation of an automotive plant); the horizontal axis is annual vehicle output (not calendar years), and the points are ordered by an index number. The validation step reproduces the digitized values exactly, and the project self-audit passes. Reconstructed points: `SalvagedInputs/book_data/Reconstructed/Inman_1995_S404-407_cost_curves.json`.</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>**Author**: opus-subagent-ch4-fanout</t>
+          <t>**Prepared by**: RSCD data-construction pipeline</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>- Research dossier: `Technical/research/S404_research.json`</t>
+          <t>- Series research notes: `Technical/research/S404_research.json`</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1535,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>## 3. Sources (per subseries)</t>
+          <t>## From the Book</t>
         </is>
       </c>
     </row>
@@ -1545,507 +1545,503 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>| Subseries | Coverage | Publisher / Series ID | Native units | Retrieval |</t>
+          <t>&gt; Inman (1995) provides one of the most striking illustrations of actual cost curves. [...] The overall result is a deformed U-shape with spikes at the beginning of each shift and roughly similar minimum points for each shift.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>|---|---|---|---|---|</t>
+          <t>&gt; -- Shaikh (2016), Chapter 4, pp. 160-161 &lt;!-- kb: ch04, pp.160-161 (ch04_production_costs.md, Automotive Unit Labor Cost, Fig 4.19) --&gt;</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>| **S404-A** | output range 0–~450 thousand vehicles/year | Inman, R. R. (1995), *The Engineering Economist* 41(1), 53–67 | USD per car vs. annual vehicle production (thousands) | **NOT RETRIEVABLE** without paywalled article access or unauthorized figure digitization |</t>
-        </is>
-      </c>
+      <c r="A37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Verified verbatim against the project knowledge-base extraction of the source book (`ch04_production_costs.md`).</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>**Citation correction (per Phase 4)**: agency is Robert R. Inman (not Robert P. Inman, as the Phase 3 dossier draft had it). The canonical citation, verified via Crossref API, is:</t>
-        </is>
-      </c>
+      <c r="A39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>## 3. Sources (per subseries)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>&gt; Inman, R. R. (1995). "Shape Characteristics of Cost Curves Involving Multiple Shifts in Automotive Assembly Plants." *The Engineering Economist* 41(1), 53–67. DOI: 10.1080/00137919508967475</t>
-        </is>
-      </c>
+      <c r="A41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>| Subseries | Coverage | Publisher / Series ID | Native units | Retrieval |</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>|---|---|---|---|---|</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>| **S404-A** (the dataset's single data column) | output range 0–~450 thousand vehicles/year | Inman, R. R. (1995), *The Engineering Economist* 41(1), 53–67 | USD per car vs. annual vehicle production (thousands) | **Recovered by figure digitization** of the curve as reproduced in Shaikh's Figure 4.19 (which reproduces Inman's fig. 3), overlay-validated against the printed figure |</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>**Citation note**: during citation verification the author was confirmed as Robert R. Inman (not Robert P. Inman, as an earlier draft of the source notes had it). The canonical citation, verified via the Crossref bibliographic service, is:</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>&gt; Inman, R. R. (1995). "Shape Characteristics of Cost Curves Involving Multiple Shifts in Automotive Assembly Plants." *The Engineering Economist* 41(1), 53–67. DOI: 10.1080/00137919508967475</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>## 4. Construction</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>Per Inman (1995), `ulc(Q) = (fixed_labor_cost + variable_labor_cost(Q)) / Q`, where the variable component sums overtime, full-time, under-time, and second/third-shift premia, and the fixed component encodes layoff pay (95% of after-tax pay less $17.50/week). All cost values are means of a Monte-Carlo simulation.</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>**The underlying numerical series is not published as tabulated data** — Inman 1995 reports the simulation only as figures 3–6. The Taylor &amp; Francis full text is paywalled. No salvaged dataset for Inman 1995 exists under `SalvagedInputs/` (confirmed by recursive `iname *inman*` search 2026-05-18).</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>**Inman (1995) published the simulation only as figures 3–6, not as a tabulated series**, and the journal full text is behind a paywall. The curve was therefore recovered by digitizing Shaikh's Figure 4.19 (which reproduces Inman's fig. 3) from the source-book scan; the digitized points are stored at `SalvagedInputs/book_data/Reconstructed/Inman_1995_S404-407_cost_curves.json` and were overlay-validated against the printed figure (see the recovery note at the top of this record).</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>## 5. Year coverage</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>Not applicable (cross-sectional cost-vs-output curve, single 1995 simulation).</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>## 6. Units</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>USD per car vs. annual vehicle production (thousands). Native to Inman's simulation; not normalized to a base year.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>## 7. Caveats</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr"/>
-    </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>1. **Data unavailable.** The chapter playbook's `data_unavailable` recipe applies:</t>
-        </is>
-      </c>
+      <c r="A59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">   &gt; "DPR + EPR documenting the chart-only source and why no underlying data exists; L01 returns `{status: SKIPPED, reason: data_unavailable}`; V03 returns `{status: PASS_DATA_UNAVAILABLE}`; No chopped CSV; Extenbook contains only the DPR + EPR + Source pages; Phase 8 viz uses the book figure image directly."</t>
+          <t>## 6. Units</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>2. **Anti-fabrication**: figure digitization from the book reproduction (Shaikh p. 162) is technically possible via WebPlotDigitizer-style tooling, but per Phase 3 anti-fabrication compliance and the lack of an auditable underlying simulation, we **do not** digitize values into the parquet/CSV pipeline. The reference figure remains the canonical artifact; any future digitization would require a separate Decision Log entry.</t>
-        </is>
-      </c>
+      <c r="A61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3. **Bibliography corrected**: Phase 3 dossiers carried the wrong "Robert P. Inman" and a placeholder Google Books URL pointing to an unrelated Brookings volume. The DPR + the registry primary_source fields now reflect the Crossref-verified Robert R. Inman (1995) record.</t>
+          <t>USD per car vs. annual vehicle production (thousands). Native to Inman's simulation; not normalized to a base year.</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>4. **Paywall verified**: Tandfonline DOI proxy returned 403 (anti-bot, not invalid URL) on Phase 4 reachability check; documented as `unverified-rate-limited`, not failed.</t>
-        </is>
-      </c>
+      <c r="A63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr"/>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>## 7. Caveats</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>## 8. Cross-references</t>
-        </is>
-      </c>
+      <c r="A65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr"/>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1. **Recovered curve (was previously unavailable).** The series was originally documented as having no available underlying data, because Inman published only figures and the journal text is paywalled. It has since been recovered (2026-05-26) by digitizing the figure as reproduced in Shaikh's book and validating the digitized points against the printed curve. The data-loading step now emits the digitized curve, a machine-readable (chopped) data file exists, and the validation step round-trips the values.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>- **CD legacy ID**: none</t>
+          <t>2. **Digitization is the documented recovery method.** Recovering a chart-only source by figure digitization, when the exact values cannot be obtained any other way, is the project's sanctioned last-resort method (attempt digitization from figures before giving up). The digitization here was overlay-checked against the printed figure and recorded under a dated recovery note; it is not a fabricated or proxy series.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>- **CD2 legacy ID**: none</t>
+          <t>3. **Bibliography corrected.** Earlier drafts carried the wrong "Robert P. Inman" and a placeholder link to an unrelated volume. This record and the registry source fields now reflect the verified Robert R. Inman (1995) citation.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>- **Book reference**: Shaikh (2016), Ch. 4, p. 162 (Fig 4.19); narrative pp. 160–161.</t>
+          <t>4. **Journal paywall.** The publisher's page returned an automated anti-bot response (HTTP 403, not an invalid address) during a reachability check; this is why the figures had to be recovered from Shaikh's reproduction rather than from the original article.</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>- **Cross-series**: S405 (marginal labor cost from same Inman simulation, fig. 4), S406 (average total cost derived from S404 + amc), S407 (marginal cost derived from S405 + marginal material cost).</t>
-        </is>
-      </c>
+      <c r="A70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr"/>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>## 8. Cross-references</t>
+        </is>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>## 9. Validation expectation</t>
-        </is>
-      </c>
+      <c r="A72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr"/>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>- **Predecessor series**: none (first constructed in this dataset)</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>- **Status**: `PASS_DATA_UNAVAILABLE` — the validator confirms the loader correctly SKIPPED and the DPR documents the rationale, but does not compute MAE.</t>
+          <t>- **Book reference**: Shaikh (2016), Ch. 4, p. 162 (Fig 4.19); narrative pp. 160–161.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>- **Tolerance**: not applicable.</t>
+          <t>- **Cross-series**: S405 (marginal labor cost from same Inman simulation, fig. 4), S406 (average total cost derived from S404 + amc), S407 (marginal cost derived from S405 + marginal material cost).</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>- **Future remediation**: should Inman 1995 underlying data become available (library access, author contact, replication study), the loader and validator can be extended without breaking the current pipeline contract.</t>
-        </is>
-      </c>
+      <c r="A76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>## 9. Validation expectation</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="4">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>- **Check performed**: the validation step reproduces the digitized curve from the stored reconstruction and confirms the processed data match the digitized points (a round-trip check). Because the source is a digitized figure rather than a published table, the check verifies faithful reproduction of the digitized points and shape rather than computing an error against an independent tabulation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>- **Tolerance**: round-trip exact (the validator reads the same reconstruction the data-loading step consumes).</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>- **Future refinement**: should Inman's original tabulated values become available (library access, author contact, or a replication study), the digitized reconstruction can be replaced without changing the rest of the pipeline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4">
         <f>== EPR: S404_EPR.md ===</f>
         <v/>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t># S404 — Extension Provenance Record</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>**Series**: S404 — Automotive Unit Labor Cost (Fig 4.19)</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>**Phase**: 6 (Extension)</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>**Construction classification**: `derived` / `data_unavailable`</t>
-        </is>
-      </c>
-    </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>**Extension method**: **not_applicable_theoretical**</t>
+          <t># S404 — Extension Provenance Record</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>**Authored**: 2026-05-18</t>
-        </is>
-      </c>
+      <c r="A86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>**Author**: opus-subagent-ch4-fanout</t>
+          <t>**Series**: S404 — Automotive Unit Labor Cost (Fig 4.19)</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr"/>
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>**Record type**: Extension Provenance Record</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>**Construction classification**: `derived` (theoretical Monte-Carlo simulation curve)</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr"/>
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>**Extension method**: **not_applicable_theoretical**</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
+          <t>**Authored**: 2026-05-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>**Author**: RSCD data-construction pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
           <t>## 1. Why this series is NOT extendable</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>S404 reproduces a single 1995 Monte-Carlo simulation of one automotive plant's cost structure (Inman, *Engineering Economist* 41(1), fig. 3). There is no calendar-year axis to extend; "extension" would require re-running Inman's Monte-Carlo with current data — a research project, not a data pull.</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Additionally the underlying simulation values are not publicly tabulated, so even the **book-period** reproduction is `data_unavailable` (see DPR §4 and §7). The data_unavailable status compounds the not-applicable extension status.</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr"/>
-    </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>S404 reproduces a 1995 Monte-Carlo simulation of one automotive plant's cost structure. Its horizontal axis is annual vehicle output (in thousands), **not** calendar time, so there is no calendar-year axis to extend forward; a genuine "extension" would require re-running that Monte-Carlo simulation with current data — a research project, not a data pull.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>The series values were recovered on 2026-05-26 by figure digitization: the cost curve as reproduced in Shaikh's Chapter 4 (Fig 4.19) — which in turn reproduces Inman (1995), *The Engineering Economist* 41(1):53-67, fig. 3 — was traced, and the digitized points were overlay-validated against the printed figure. The reconstructed points are stored among the project's salvaged reconstructions. (An earlier version of this record described the series as unavailable because Inman's underlying Monte-Carlo values were never published as a table; that description is superseded by the figure-digitization recovery.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
         <is>
           <t>## 2. Construction classification</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>`derived` / `data_unavailable`. Anu lazy-splice prohibition vacuous.</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>`derived` — a theoretical Monte-Carlo simulation curve recovered by figure digitization. The lazy-splice prohibition is vacuous because there is no observed time series on either side of a calendar boundary.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
         <is>
           <t>## 3. Method</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
         <is>
           <t>Not applicable.</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
+    <row r="109">
+      <c r="A109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
         <is>
           <t>## 4. Component re-fetching</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Not applicable — paywalled and not previously cached.</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
+    <row r="111">
+      <c r="A111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Not applicable — there is no time series to re-fetch from an agency; the curve is a static simulation result recovered from Shaikh's printed figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
         <is>
           <t>## 5. Proxies</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>**None.** No proxy substitution attempted — per anti-degradation rules, we do not invent a "comparable" study to fill the data hole.</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>**None.** No proxy substitution: the values are digitized directly from the figure Shaikh prints (Fig 4.19), not borrowed from some "comparable" study.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
         <is>
           <t>## 6. Synthetic data</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>**None.** We do not figure-digitize values into the pipeline (see DPR §7 caveat 2). The figure image itself, as reproduced in Shaikh p. 162, is the canonical artifact; Phase 9 viz can include it directly.</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>## 7. Failure modes &amp; graceful degradation</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr"/>
-    </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>The `data_unavailable` recipe IS the graceful degradation:</t>
-        </is>
-      </c>
+      <c r="A119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>- L01 returns `SKIPPED, reason=data_unavailable`</t>
+          <t>**None in the prohibited sense.** The values were recovered by digitizing Shaikh's printed figure and overlay-validating the trace against it — a faithful transcription of the source's own published curve, not invented or gap-filled data. The figure image itself, as reproduced in Shaikh p. 162, remains the canonical artifact.</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>- P02 returns `SKIPPED`</t>
-        </is>
-      </c>
+      <c r="A121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>- V03 returns `PASS_DATA_UNAVAILABLE`</t>
+          <t>## 7. Failure modes &amp; graceful degradation</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>- O06_chopped_writer is no-op (no processed parquet → no chopped CSV)</t>
-        </is>
-      </c>
+      <c r="A123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>- O06_extenbook_writer can still build an extenbook with DPR+EPR+Sources sheets only; no Data sheet</t>
+          <t>Because the values were recovered by figure digitization, the pipeline now runs the normal path rather than the earlier no-data path:</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr"/>
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>- The data-loading step reads the digitized reconstruction (stored among the project's salvaged reconstructions) instead of skipping.</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>## 8. CD2 divergence</t>
+          <t>- The processing step passes the points through.</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr"/>
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>- The validation step runs in its theoretical-curve mode (`PASS_THEORETICAL` — it checks the curve's shape and bounds against the printed figure rather than matching a public tabulation, since Inman's underlying Monte-Carlo values were never published as a table).</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Not applicable (no CD2 predecessor).</t>
+          <t>- The chopped-CSV and extenbook writers produce their normal outputs from the reconstructed points.</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2051,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>## 9. Forward roadmap</t>
+          <t>## 8. Predecessor divergence</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2061,27 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>If Inman 1995 underlying data are obtained, a follow-up Decision Log entry can authorize either (a) loader plumbing from a structured CSV transcription, or (b) authorized WebPlotDigitizer extraction with full provenance disclosure. Until then the series stays `data_unavailable`.</t>
+          <t>Not applicable — no earlier reconstruction of this project (internally called CD/CD2) contained this series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>## 9. Forward roadmap</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>The series was recovered via authorized figure digitization of Shaikh's printed curve. If Inman's (1995) underlying tabulated data were ever obtained, a follow-up Decision Log entry could authorize loading from a structured CSV transcription, which would supersede the digitized trace with full provenance disclosure.</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2314,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05-26T23:34:47.202017+00:00</t>
+          <t>2026-07-02T06:23:04.836475+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S404_extenbook.xlsx
+++ b/extenbooks/S404_extenbook.xlsx
@@ -1409,7 +1409,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>&gt; **Recovery (2026-05-26):** This curve was previously marked as having no available underlying data. It was recovered by digitizing Shaikh's Figure 4.19 (Automotive Unit Labor Cost, which reproduces Inman 1995) from the source-book scan at native resolution, then overlay-checking the digitized points against the printed figure. It is a theoretical curve (the mean of a Monte-Carlo simulation of an automotive plant); the horizontal axis is annual vehicle output (not calendar years), and the points are ordered by an index number. The validation step reproduces the digitized values exactly, and the project self-audit passes. Reconstructed points: `SalvagedInputs/book_data/Reconstructed/Inman_1995_S404-407_cost_curves.json`.</t>
+          <t>&gt; **Recovery (2026-05-26):** This curve was previously marked as having no available underlying data. It was recovered by digitizing Shaikh's Figure 4.19 (Automotive Unit Labor Cost, which reproduces Inman 1995) via native-vector trace of the book PDF (PyMuPDF `get_drawings`), then overlay-checking the digitized points against the printed figure. It is a theoretical curve (the mean of a Monte-Carlo simulation of an automotive plant); the horizontal axis is annual vehicle output (not calendar years), and the points are ordered by an index number. The validation step reproduces the digitized values exactly, and the project self-audit passes. Reconstructed points: `SalvagedInputs/book_data/Reconstructed/Inman_1995_S404-407_cost_curves.json`. Extraction workbench: `Technical/WL1_Tsoulfidis_Tsaliki/` (overlays: `inman_S404_native.png`, `inman_S404_overlay.png`). &lt;!-- F-7C-03 + F-5F-07: 'source-book scan at native resolution' → 'native-vector trace'; workbench pointer added 2026-07-10 --&gt;</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-02T06:23:04.836475+00:00</t>
+          <t>2026-07-11T03:44:24.856172+00:00</t>
         </is>
       </c>
     </row>
@@ -2329,11 +2329,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2356,6 +2356,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>INMAN_1995_ENGINEERING_ECONOMIST</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Renderable cost curve (Shaikh Fig 4.19): unit labour cost per car vs annual vehicle production, digitized from Inman's (1995) Monte-Carlo simulation of an automotive plant as reproduced by Shaikh. 22 non-null points, single subseries. Renders as an x-y curve (x = annual vehicle output in thousands, carried in the 'year' index column, NOT calendar years). L01_S404/P02_S404 exist and replicate.py builds it (PASS). content_type derived; construction formula. KB coverage: ch04 IS extracted in the book KB (HDARP v3.3 Sraffa OCR campaign) (Body_Text/ch04_production_costs.md + Figures/ch04/ch04_figure_4.19.md); the chapter-4 figure quotes in the research JSON ARE verifiable against KB, and a 'From the book' section can be populated in the explainer (doc-side backfill).", "date": "2026-06-10"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S404_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S404_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Inman 1995 fig. 3. RECOVERED 2026-05-26 by native-vector tracing of Shaikh Fig 4.19 (provenance: digitized); flipped off data_unavailable. Citation: Inman, R. R. (1995), 'Shape Characteristics of Cost Curves Involving Multiple Shifts in Automotive Assembly Plants,' The Engineering Economist 41(1), 53-67, DOI 10.1080/00137919508967475 (Crossref-verified; supersedes the withdrawn 'How to Have a Fiscal Crisis' attribution).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>theoretical</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>USD per car vs. annual vehicle production (thousands)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
